--- a/Versão5/GEOT/Ontologia_Geotécnica.xlsx
+++ b/Versão5/GEOT/Ontologia_Geotécnica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GEOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CCE182-FA99-4715-B5E9-ACBE3D818A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1C2048-A25C-4C61-8009-0CD94B4AD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -497,12 +497,6 @@
     <t>Tipo de método de compactação que adota máquinas de rolamento.</t>
   </si>
   <si>
-    <t>Método que aplica carga à fundação para descarregar água dos poros, e a ela é consolidada.</t>
-  </si>
-  <si>
-    <t>Método para definir medidas de drenagem vertical na fundação, de modo que a água dos poros do sol.</t>
-  </si>
-  <si>
     <t>Elementos de estacionamento.</t>
   </si>
   <si>
@@ -1142,9 +1136,6 @@
     <t>Un método que aplica una carga a los cimientos para expulsar el agua por los poros, y que se consolida en ella.</t>
   </si>
   <si>
-    <t>Método para colocar medidas verticales de drenaje en los cimientos, de modo que el agua de los poros del sol llegue a la superficie.</t>
-  </si>
-  <si>
     <t>El vacío resultante de la modificación del terreno existente o la estructura vial mediante excavaciones.</t>
   </si>
   <si>
@@ -1233,6 +1224,15 @@
   </si>
   <si>
     <t>Vegetación o cobertura vegetal (de una zona).</t>
+  </si>
+  <si>
+    <t>Método de compactación por drenaje.</t>
+  </si>
+  <si>
+    <t>Método de compactação por drenagem vertical.</t>
+  </si>
+  <si>
+    <t>Método que aplica carga à fundação para descarregar água dos poros.</t>
   </si>
 </sst>
 </file>
@@ -1861,13 +1861,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2249,11 +2247,63 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2304,61 +2354,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2876,7 +2876,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C3" s="55" t="s">
         <v>94</v>
@@ -3032,7 +3032,7 @@
         <v>65</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C17" s="55" t="s">
         <v>94</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B18" s="33">
         <f ca="1">NOW()</f>
-        <v>46136.792517592592</v>
+        <v>46136.803978819444</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>94</v>
@@ -3112,7 +3112,7 @@
         <v>69</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C24" s="55" t="s">
         <v>94</v>
@@ -3123,7 +3123,7 @@
         <v>70</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C25" s="55" t="s">
         <v>95</v>
@@ -3250,7 +3250,7 @@
         <v>86</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z1" s="62" t="s">
         <v>89</v>
@@ -3331,7 +3331,7 @@
         <v>Informação</v>
       </c>
       <c r="V2" s="27" t="str">
-        <f t="shared" ref="V2:V52" si="0">SUBSTITUTE(C2, "_", " ")</f>
+        <f t="shared" ref="V2:V3" si="0">SUBSTITUTE(C2, "_", " ")</f>
         <v>Gestão</v>
       </c>
       <c r="W2" s="1" t="str">
@@ -3348,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
@@ -3359,16 +3359,16 @@
         <v>43</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>9</v>
@@ -3386,19 +3386,19 @@
         <v>9</v>
       </c>
       <c r="L3" s="26" t="str">
-        <f t="shared" ref="L3:L28" si="1">CONCATENATE("", C3)</f>
+        <f t="shared" ref="L3" si="1">CONCATENATE("", C3)</f>
         <v>GeoTécnico</v>
       </c>
       <c r="M3" s="26" t="str">
-        <f t="shared" ref="M3:M28" si="2">CONCATENATE("", D3)</f>
+        <f t="shared" ref="M3" si="2">CONCATENATE("", D3)</f>
         <v>Elementos.de.Solo</v>
       </c>
       <c r="N3" s="26" t="str">
-        <f t="shared" ref="N3:N28" si="3">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N3" si="3">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
         <v>Compactação</v>
       </c>
       <c r="O3" s="26" t="str">
-        <f t="shared" ref="O3:O28" si="4">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O3" si="4">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
         <v>Solo Reforçado</v>
       </c>
       <c r="P3" s="21" t="s">
@@ -3431,16 +3431,16 @@
         <v>Key-GEO-3</v>
       </c>
       <c r="X3" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y3" s="35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Z3" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3451,16 +3451,16 @@
         <v>43</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G4" s="52" t="s">
         <v>9</v>
@@ -3497,7 +3497,7 @@
         <v>137</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R4" s="47" t="s">
         <v>9</v>
@@ -3523,16 +3523,16 @@
         <v>Key-GEO-4</v>
       </c>
       <c r="X4" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y4" s="35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Z4" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3543,16 +3543,16 @@
         <v>43</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G5" s="52" t="s">
         <v>9</v>
@@ -3589,7 +3589,7 @@
         <v>138</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="R5" s="47" t="s">
         <v>9</v>
@@ -3615,16 +3615,16 @@
         <v>Key-GEO-5</v>
       </c>
       <c r="X5" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y5" s="35" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z5" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3635,16 +3635,16 @@
         <v>43</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G6" s="52" t="s">
         <v>9</v>
@@ -3681,7 +3681,7 @@
         <v>139</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R6" s="47" t="s">
         <v>9</v>
@@ -3707,16 +3707,16 @@
         <v>Key-GEO-6</v>
       </c>
       <c r="X6" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y6" s="35" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Z6" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3727,16 +3727,16 @@
         <v>43</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G7" s="52" t="s">
         <v>9</v>
@@ -3773,7 +3773,7 @@
         <v>140</v>
       </c>
       <c r="Q7" s="34" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="R7" s="47" t="s">
         <v>9</v>
@@ -3799,16 +3799,16 @@
         <v>Key-GEO-7</v>
       </c>
       <c r="X7" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y7" s="35" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Z7" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA7" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3819,16 +3819,16 @@
         <v>43</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G8" s="52" t="s">
         <v>9</v>
@@ -3862,10 +3862,10 @@
         <v>Solo Reforçado PréCarregado</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>141</v>
+        <v>386</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="R8" s="47" t="s">
         <v>9</v>
@@ -3891,16 +3891,16 @@
         <v>Key-GEO-8</v>
       </c>
       <c r="X8" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y8" s="35" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z8" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3911,16 +3911,16 @@
         <v>43</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G9" s="52" t="s">
         <v>9</v>
@@ -3954,10 +3954,10 @@
         <v>Solo Reforçado Drenado</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>142</v>
+        <v>385</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="R9" s="47" t="s">
         <v>9</v>
@@ -3983,16 +3983,16 @@
         <v>Key-GEO-9</v>
       </c>
       <c r="X9" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y9" s="35" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Z9" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA9" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4003,16 +4003,16 @@
         <v>43</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G10" s="52" t="s">
         <v>9</v>
@@ -4049,7 +4049,7 @@
         <v>104</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="R10" s="47" t="s">
         <v>9</v>
@@ -4075,16 +4075,16 @@
         <v>Key-GEO-10</v>
       </c>
       <c r="X10" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y10" s="35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Z10" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA10" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4095,16 +4095,16 @@
         <v>43</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>9</v>
@@ -4141,7 +4141,7 @@
         <v>105</v>
       </c>
       <c r="Q11" s="34" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="R11" s="47" t="s">
         <v>9</v>
@@ -4167,16 +4167,16 @@
         <v>Key-GEO-11</v>
       </c>
       <c r="X11" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y11" s="35" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z11" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA11" s="21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4187,16 +4187,16 @@
         <v>43</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G12" s="52" t="s">
         <v>9</v>
@@ -4233,7 +4233,7 @@
         <v>106</v>
       </c>
       <c r="Q12" s="34" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="R12" s="47" t="s">
         <v>9</v>
@@ -4259,16 +4259,16 @@
         <v>Key-GEO-12</v>
       </c>
       <c r="X12" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y12" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Z12" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4279,16 +4279,16 @@
         <v>43</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G13" s="52" t="s">
         <v>9</v>
@@ -4325,7 +4325,7 @@
         <v>107</v>
       </c>
       <c r="Q13" s="34" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="R13" s="47" t="s">
         <v>9</v>
@@ -4351,16 +4351,16 @@
         <v>Key-GEO-13</v>
       </c>
       <c r="X13" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y13" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Z13" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4371,16 +4371,16 @@
         <v>43</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G14" s="52" t="s">
         <v>9</v>
@@ -4443,16 +4443,16 @@
         <v>Key-GEO-14</v>
       </c>
       <c r="X14" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y14" s="35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Z14" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA14" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4463,16 +4463,16 @@
         <v>43</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G15" s="52" t="s">
         <v>9</v>
@@ -4509,7 +4509,7 @@
         <v>110</v>
       </c>
       <c r="Q15" s="34" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="R15" s="47" t="s">
         <v>9</v>
@@ -4535,16 +4535,16 @@
         <v>Key-GEO-15</v>
       </c>
       <c r="X15" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y15" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z15" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA15" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4555,16 +4555,16 @@
         <v>43</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G16" s="52" t="s">
         <v>9</v>
@@ -4601,7 +4601,7 @@
         <v>111</v>
       </c>
       <c r="Q16" s="34" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="R16" s="47" t="s">
         <v>9</v>
@@ -4627,16 +4627,16 @@
         <v>Key-GEO-16</v>
       </c>
       <c r="X16" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y16" s="35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Z16" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA16" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4647,16 +4647,16 @@
         <v>43</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G17" s="52" t="s">
         <v>9</v>
@@ -4693,7 +4693,7 @@
         <v>112</v>
       </c>
       <c r="Q17" s="34" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="R17" s="47" t="s">
         <v>9</v>
@@ -4719,16 +4719,16 @@
         <v>Key-GEO-17</v>
       </c>
       <c r="X17" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y17" s="35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Z17" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA17" s="21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4739,16 +4739,16 @@
         <v>43</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G18" s="52" t="s">
         <v>9</v>
@@ -4785,7 +4785,7 @@
         <v>113</v>
       </c>
       <c r="Q18" s="34" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="R18" s="47" t="s">
         <v>9</v>
@@ -4811,16 +4811,16 @@
         <v>Key-GEO-18</v>
       </c>
       <c r="X18" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y18" s="35" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z18" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA18" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4831,16 +4831,16 @@
         <v>43</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G19" s="52" t="s">
         <v>9</v>
@@ -4877,7 +4877,7 @@
         <v>114</v>
       </c>
       <c r="Q19" s="34" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="R19" s="47" t="s">
         <v>9</v>
@@ -4903,16 +4903,16 @@
         <v>Key-GEO-19</v>
       </c>
       <c r="X19" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y19" s="35" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Z19" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA19" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4923,16 +4923,16 @@
         <v>43</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F20" s="25" t="s">
         <v>252</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>254</v>
       </c>
       <c r="G20" s="52" t="s">
         <v>9</v>
@@ -4969,7 +4969,7 @@
         <v>115</v>
       </c>
       <c r="Q20" s="34" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R20" s="47" t="s">
         <v>9</v>
@@ -4995,13 +4995,13 @@
         <v>Key-GEO-20</v>
       </c>
       <c r="X20" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y20" s="35" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z20" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA20" s="21" t="s">
         <v>116</v>
@@ -5015,16 +5015,16 @@
         <v>43</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>253</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>255</v>
       </c>
       <c r="G21" s="52" t="s">
         <v>9</v>
@@ -5061,7 +5061,7 @@
         <v>117</v>
       </c>
       <c r="Q21" s="34" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="R21" s="47" t="s">
         <v>9</v>
@@ -5087,16 +5087,16 @@
         <v>Key-GEO-21</v>
       </c>
       <c r="X21" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y21" s="35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Z21" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA21" s="21" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5107,16 +5107,16 @@
         <v>43</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G22" s="52" t="s">
         <v>9</v>
@@ -5153,7 +5153,7 @@
         <v>118</v>
       </c>
       <c r="Q22" s="34" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R22" s="47" t="s">
         <v>9</v>
@@ -5179,16 +5179,16 @@
         <v>Key-GEO-22</v>
       </c>
       <c r="X22" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y22" s="35" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z22" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA22" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5199,16 +5199,16 @@
         <v>43</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G23" s="52" t="s">
         <v>9</v>
@@ -5245,7 +5245,7 @@
         <v>119</v>
       </c>
       <c r="Q23" s="34" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="R23" s="47" t="s">
         <v>9</v>
@@ -5271,16 +5271,16 @@
         <v>Key-GEO-23</v>
       </c>
       <c r="X23" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y23" s="35" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Z23" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA23" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5291,16 +5291,16 @@
         <v>43</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G24" s="52" t="s">
         <v>9</v>
@@ -5337,7 +5337,7 @@
         <v>120</v>
       </c>
       <c r="Q24" s="34" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="R24" s="47" t="s">
         <v>9</v>
@@ -5363,16 +5363,16 @@
         <v>Key-GEO-24</v>
       </c>
       <c r="X24" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y24" s="35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Z24" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA24" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5383,16 +5383,16 @@
         <v>43</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G25" s="52" t="s">
         <v>9</v>
@@ -5429,7 +5429,7 @@
         <v>121</v>
       </c>
       <c r="Q25" s="34" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R25" s="47" t="s">
         <v>9</v>
@@ -5455,16 +5455,16 @@
         <v>Key-GEO-25</v>
       </c>
       <c r="X25" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y25" s="35" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Z25" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA25" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5475,16 +5475,16 @@
         <v>43</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G26" s="52" t="s">
         <v>9</v>
@@ -5521,7 +5521,7 @@
         <v>122</v>
       </c>
       <c r="Q26" s="34" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R26" s="47" t="s">
         <v>9</v>
@@ -5547,16 +5547,16 @@
         <v>Key-GEO-26</v>
       </c>
       <c r="X26" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y26" s="35" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z26" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA26" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5567,16 +5567,16 @@
         <v>43</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G27" s="52" t="s">
         <v>9</v>
@@ -5613,7 +5613,7 @@
         <v>123</v>
       </c>
       <c r="Q27" s="34" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R27" s="47" t="s">
         <v>9</v>
@@ -5639,16 +5639,16 @@
         <v>Key-GEO-27</v>
       </c>
       <c r="X27" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y27" s="35" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Z27" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA27" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5659,16 +5659,16 @@
         <v>43</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G28" s="52" t="s">
         <v>9</v>
@@ -5705,7 +5705,7 @@
         <v>124</v>
       </c>
       <c r="Q28" s="34" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="R28" s="47" t="s">
         <v>9</v>
@@ -5731,16 +5731,16 @@
         <v>Key-GEO-28</v>
       </c>
       <c r="X28" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y28" s="35" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z28" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA28" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5751,16 +5751,16 @@
         <v>43</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E29" s="64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F29" s="64" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G29" s="52" t="s">
         <v>9</v>
@@ -5794,10 +5794,10 @@
         <v>Ponto Interno</v>
       </c>
       <c r="P29" s="48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q29" s="34" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="R29" s="47" t="s">
         <v>9</v>
@@ -5823,16 +5823,16 @@
         <v>Key-GEO-29</v>
       </c>
       <c r="X29" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y29" s="27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z29" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA29" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5843,16 +5843,16 @@
         <v>43</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E30" s="64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F30" s="64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G30" s="52" t="s">
         <v>9</v>
@@ -5886,10 +5886,10 @@
         <v>Ponto Perimetral</v>
       </c>
       <c r="P30" s="48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q30" s="34" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="R30" s="47" t="s">
         <v>9</v>
@@ -5915,16 +5915,16 @@
         <v>Key-GEO-30</v>
       </c>
       <c r="X30" s="27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Y30" s="27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z30" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA30" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5935,16 +5935,16 @@
         <v>43</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E31" s="64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F31" s="64" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G31" s="52" t="s">
         <v>9</v>
@@ -5978,10 +5978,10 @@
         <v>Ponto Região</v>
       </c>
       <c r="P31" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q31" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R31" s="47" t="s">
         <v>9</v>
@@ -6007,16 +6007,16 @@
         <v>Key-GEO-31</v>
       </c>
       <c r="X31" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Y31" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z31" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA31" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6027,16 +6027,16 @@
         <v>43</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F32" s="64" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G32" s="52" t="s">
         <v>9</v>
@@ -6070,10 +6070,10 @@
         <v>Ponto Superfície</v>
       </c>
       <c r="P32" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q32" s="34" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="R32" s="47" t="s">
         <v>9</v>
@@ -6099,16 +6099,16 @@
         <v>Key-GEO-32</v>
       </c>
       <c r="X32" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y32" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="Y32" s="21" t="s">
-        <v>221</v>
-      </c>
       <c r="Z32" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA32" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6119,16 +6119,16 @@
         <v>43</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F33" s="64" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G33" s="52" t="s">
         <v>9</v>
@@ -6191,16 +6191,16 @@
         <v>Key-GEO-33</v>
       </c>
       <c r="X33" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y33" s="35" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Z33" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6211,16 +6211,16 @@
         <v>43</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F34" s="64" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G34" s="52" t="s">
         <v>9</v>
@@ -6283,16 +6283,16 @@
         <v>Key-GEO-34</v>
       </c>
       <c r="X34" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y34" s="35" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Z34" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA34" s="21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6303,16 +6303,16 @@
         <v>43</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E35" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F35" s="64" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G35" s="52" t="s">
         <v>9</v>
@@ -6346,10 +6346,10 @@
         <v>Topografia Sólida</v>
       </c>
       <c r="P35" s="48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q35" s="34" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="R35" s="47" t="s">
         <v>9</v>
@@ -6375,16 +6375,16 @@
         <v>Key-GEO-35</v>
       </c>
       <c r="X35" s="27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Y35" s="27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z35" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA35" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6395,16 +6395,16 @@
         <v>43</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E36" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F36" s="64" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G36" s="52" t="s">
         <v>9</v>
@@ -6438,10 +6438,10 @@
         <v>Topografia Malha</v>
       </c>
       <c r="P36" s="48" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Q36" s="34" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="R36" s="47" t="s">
         <v>9</v>
@@ -6467,16 +6467,16 @@
         <v>Key-GEO-36</v>
       </c>
       <c r="X36" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y36" s="27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z36" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA36" s="21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6487,16 +6487,16 @@
         <v>43</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E37" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F37" s="64" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G37" s="52" t="s">
         <v>9</v>
@@ -6530,10 +6530,10 @@
         <v>Topografia Sólida Núcleo</v>
       </c>
       <c r="P37" s="48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q37" s="34" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="R37" s="47" t="s">
         <v>9</v>
@@ -6559,16 +6559,16 @@
         <v>Key-GEO-37</v>
       </c>
       <c r="X37" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y37" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z37" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA37" s="21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6579,16 +6579,16 @@
         <v>43</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E38" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F38" s="64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G38" s="52" t="s">
         <v>9</v>
@@ -6622,10 +6622,10 @@
         <v>Topografia Sólida Substrato</v>
       </c>
       <c r="P38" s="48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q38" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R38" s="47" t="s">
         <v>9</v>
@@ -6651,16 +6651,16 @@
         <v>Key-GEO-38</v>
       </c>
       <c r="X38" s="27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y38" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z38" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA38" s="21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6671,16 +6671,16 @@
         <v>43</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E39" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F39" s="64" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G39" s="52" t="s">
         <v>9</v>
@@ -6714,10 +6714,10 @@
         <v>Topografia Sólida Membrana</v>
       </c>
       <c r="P39" s="48" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q39" s="34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R39" s="47" t="s">
         <v>9</v>
@@ -6743,16 +6743,16 @@
         <v>Key-GEO-39</v>
       </c>
       <c r="X39" s="27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y39" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z39" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA39" s="21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6763,16 +6763,16 @@
         <v>43</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E40" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F40" s="64" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G40" s="52" t="s">
         <v>9</v>
@@ -6806,10 +6806,10 @@
         <v>Topografia Sólida Isolamento</v>
       </c>
       <c r="P40" s="48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q40" s="34" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R40" s="47" t="s">
         <v>9</v>
@@ -6835,16 +6835,16 @@
         <v>Key-GEO-40</v>
       </c>
       <c r="X40" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y40" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z40" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA40" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6855,16 +6855,16 @@
         <v>43</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E41" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F41" s="64" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G41" s="52" t="s">
         <v>9</v>
@@ -6898,10 +6898,10 @@
         <v>Topografia Sólida Superfície</v>
       </c>
       <c r="P41" s="48" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q41" s="34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R41" s="47" t="s">
         <v>9</v>
@@ -6927,16 +6927,16 @@
         <v>Key-GEO-41</v>
       </c>
       <c r="X41" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Y41" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z41" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA41" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -6947,16 +6947,16 @@
         <v>43</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E42" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F42" s="64" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G42" s="52" t="s">
         <v>9</v>
@@ -6990,10 +6990,10 @@
         <v>Topografia Sólida Agua</v>
       </c>
       <c r="P42" s="48" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q42" s="34" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R42" s="47" t="s">
         <v>9</v>
@@ -7019,16 +7019,16 @@
         <v>Key-GEO-42</v>
       </c>
       <c r="X42" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Y42" s="27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Z42" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA42" s="21" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7039,16 +7039,16 @@
         <v>43</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E43" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F43" s="64" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G43" s="52" t="s">
         <v>9</v>
@@ -7085,7 +7085,7 @@
         <v>133</v>
       </c>
       <c r="Q43" s="34" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="R43" s="47" t="s">
         <v>9</v>
@@ -7111,16 +7111,16 @@
         <v>Key-GEO-43</v>
       </c>
       <c r="X43" s="35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Y43" s="35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Z43" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA43" s="21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7131,16 +7131,16 @@
         <v>43</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E44" s="64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F44" s="64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G44" s="52" t="s">
         <v>9</v>
@@ -7174,10 +7174,10 @@
         <v>Curva de 10</v>
       </c>
       <c r="P44" s="48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q44" s="34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R44" s="47" t="s">
         <v>9</v>
@@ -7203,16 +7203,16 @@
         <v>Key-GEO-44</v>
       </c>
       <c r="X44" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Y44" s="27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Z44" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA44" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7223,16 +7223,16 @@
         <v>43</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E45" s="64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F45" s="64" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G45" s="52" t="s">
         <v>9</v>
@@ -7266,10 +7266,10 @@
         <v>Curva de 05</v>
       </c>
       <c r="P45" s="48" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q45" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R45" s="47" t="s">
         <v>9</v>
@@ -7295,16 +7295,16 @@
         <v>Key-GEO-45</v>
       </c>
       <c r="X45" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Y45" s="27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Z45" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA45" s="21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7315,16 +7315,16 @@
         <v>43</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E46" s="64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F46" s="64" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G46" s="52" t="s">
         <v>9</v>
@@ -7358,10 +7358,10 @@
         <v>Curva de 01</v>
       </c>
       <c r="P46" s="48" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q46" s="34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R46" s="47" t="s">
         <v>9</v>
@@ -7387,16 +7387,16 @@
         <v>Key-GEO-46</v>
       </c>
       <c r="X46" s="27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Y46" s="27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Z46" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA46" s="21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7407,16 +7407,16 @@
         <v>43</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G47" s="52" t="s">
         <v>9</v>
@@ -7450,10 +7450,10 @@
         <v>Divisa</v>
       </c>
       <c r="P47" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q47" s="34" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="R47" s="47" t="s">
         <v>9</v>
@@ -7479,16 +7479,16 @@
         <v>Key-GEO-47</v>
       </c>
       <c r="X47" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Y47" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z47" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA47" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7499,16 +7499,16 @@
         <v>43</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G48" s="52" t="s">
         <v>9</v>
@@ -7542,10 +7542,10 @@
         <v>Divisa Segmento</v>
       </c>
       <c r="P48" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q48" s="34" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="R48" s="47" t="s">
         <v>9</v>
@@ -7571,16 +7571,16 @@
         <v>Key-GEO-48</v>
       </c>
       <c r="X48" s="61" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y48" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z48" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA48" s="21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7591,16 +7591,16 @@
         <v>43</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G49" s="52" t="s">
         <v>9</v>
@@ -7637,7 +7637,7 @@
         <v>126</v>
       </c>
       <c r="Q49" s="34" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="R49" s="47" t="s">
         <v>9</v>
@@ -7663,16 +7663,16 @@
         <v>Key-GEO-49</v>
       </c>
       <c r="X49" s="35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y49" s="35" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z49" s="47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA49" s="21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7683,16 +7683,16 @@
         <v>43</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G50" s="52" t="s">
         <v>9</v>
@@ -7755,16 +7755,16 @@
         <v>Key-GEO-50</v>
       </c>
       <c r="X50" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y50" s="35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Z50" s="47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA50" s="21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7775,10 +7775,10 @@
         <v>43</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>125</v>
@@ -7818,10 +7818,10 @@
         <v>Estacionamento</v>
       </c>
       <c r="P51" s="21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q51" s="34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="R51" s="47" t="s">
         <v>9</v>
@@ -7847,16 +7847,16 @@
         <v>Key-GEO-51</v>
       </c>
       <c r="X51" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Y51" s="35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Z51" s="47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA51" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -7867,16 +7867,16 @@
         <v>43</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G52" s="52" t="s">
         <v>9</v>
@@ -7913,7 +7913,7 @@
         <v>131</v>
       </c>
       <c r="Q52" s="34" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="R52" s="47" t="s">
         <v>9</v>
@@ -7939,13 +7939,13 @@
         <v>Key-GEO-52</v>
       </c>
       <c r="X52" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Y52" s="35" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z52" s="47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AA52" s="21" t="s">
         <v>132</v>
@@ -7956,143 +7956,117 @@
     <sortCondition ref="E1:E805"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AB1:XFD1 AB3:XFD3 B3:E3 A1:W1 P3 A53:W1048576 Z53:XFD1048576 C4:E9 D20:D28 C10:D19 C20:C52 A2:A52 AA2:AA52">
+  <conditionalFormatting sqref="A53:W1048576 A1:W1 A2:A52 AA2:AA52 B3:E3 P3 AB3:XFD3 C4:E9 C10:D19 D20:D28 C20:C52 Z53:XFD1048576">
     <cfRule type="cellIs" dxfId="62" priority="227" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="61" priority="228"/>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="61" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="220"/>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="60" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="59" priority="729"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="757"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="57" priority="737"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="744"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W53:W1048576 W1">
-    <cfRule type="duplicateValues" dxfId="55" priority="556"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="54" priority="213" operator="equal">
+  <conditionalFormatting sqref="F3:F28">
+    <cfRule type="duplicateValues" dxfId="58" priority="1015"/>
+    <cfRule type="cellIs" dxfId="57" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="53" priority="178"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="52" priority="176"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB29:XFD30 P44:P46 AB44:XFD46 P29:P30 P35:P42 AB35:XFD42 F29:F46 Q3:Q52">
-    <cfRule type="cellIs" dxfId="51" priority="94" operator="equal">
+  <conditionalFormatting sqref="F29:F46 Q3:Q52 P29:P30 AB29:XFD30 P35:P42 AB35:XFD42 P44:P46 AB44:XFD46">
+    <cfRule type="cellIs" dxfId="56" priority="94" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F46">
+    <cfRule type="duplicateValues" dxfId="55" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="994"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F47:F48">
-    <cfRule type="duplicateValues" dxfId="50" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="964"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F46">
-    <cfRule type="duplicateValues" dxfId="49" priority="994"/>
+  <conditionalFormatting sqref="F49:F52">
+    <cfRule type="duplicateValues" dxfId="51" priority="1000"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F46">
-    <cfRule type="duplicateValues" dxfId="48" priority="996"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="997"/>
+  <conditionalFormatting sqref="F53:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="50" priority="228"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53:F1048576">
+    <cfRule type="duplicateValues" dxfId="49" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="220"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W53:W1048576 W1">
+    <cfRule type="duplicateValues" dxfId="44" priority="556"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X51">
+    <cfRule type="duplicateValues" dxfId="43" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3">
-    <cfRule type="cellIs" dxfId="46" priority="57" operator="equal">
+    <cfRule type="duplicateValues" dxfId="39" priority="58"/>
+    <cfRule type="cellIs" dxfId="38" priority="57" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y3">
-    <cfRule type="duplicateValues" dxfId="45" priority="58"/>
+  <conditionalFormatting sqref="Y4">
+    <cfRule type="duplicateValues" dxfId="37" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y4">
-    <cfRule type="duplicateValues" dxfId="44" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="56"/>
+  <conditionalFormatting sqref="Y4:Y9 Y18:Y28 Y11:Y15">
+    <cfRule type="duplicateValues" dxfId="33" priority="1012"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y5:Y9 Y20:Y28 Y11:Y15">
+    <cfRule type="duplicateValues" dxfId="32" priority="1009"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y5:Y9 Y20:Y28">
+    <cfRule type="duplicateValues" dxfId="31" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y10">
+    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y11:Y15">
+    <cfRule type="duplicateValues" dxfId="25" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y16:Y17">
+    <cfRule type="duplicateValues" dxfId="21" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y18:Y19">
+    <cfRule type="duplicateValues" dxfId="13" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y20:Y28">
-    <cfRule type="duplicateValues" dxfId="40" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y5:Y9 Y20:Y28">
-    <cfRule type="duplicateValues" dxfId="39" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F28">
-    <cfRule type="cellIs" dxfId="38" priority="33" operator="equal">
+  <conditionalFormatting sqref="Z1:XFD1">
+    <cfRule type="cellIs" dxfId="7" priority="213" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X51">
-    <cfRule type="duplicateValues" dxfId="36" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X51">
-    <cfRule type="duplicateValues" dxfId="35" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X51">
-    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X51">
-    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49:F52">
-    <cfRule type="duplicateValues" dxfId="32" priority="1000"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y10">
-    <cfRule type="duplicateValues" dxfId="31" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y11:Y15">
-    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y16:Y17">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y16:Y17">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y18:Y19">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y18:Y19">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y5:Y9 Y20:Y28 Y11:Y15">
-    <cfRule type="duplicateValues" dxfId="9" priority="1009"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y4:Y9 Y18:Y28 Y11:Y15">
-    <cfRule type="duplicateValues" dxfId="8" priority="1012"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F28">
-    <cfRule type="duplicateValues" dxfId="7" priority="1015"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8422,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>82</v>
@@ -8458,16 +8432,16 @@
         <v>9</v>
       </c>
       <c r="N2" s="57" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O2" s="69" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P2" s="67" t="s">
         <v>84</v>
       </c>
       <c r="Q2" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R2" s="70" t="s">
         <v>9</v>
@@ -8497,8 +8471,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="3" priority="1019"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Versão5/GEOT/Ontologia_Geotécnica.xlsx
+++ b/Versão5/GEOT/Ontologia_Geotécnica.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GEOT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA794BDC-DAA2-4251-BFDD-8F9A959FC3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1819,63 +1819,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="67">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3160,7 +3104,7 @@
       </c>
       <c r="B18" s="32">
         <f ca="1">NOW()</f>
-        <v>46139.525502430559</v>
+        <v>46214.377684259256</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>90</v>
@@ -8395,141 +8339,129 @@
     <sortCondition ref="E1:E809"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A7:A56">
-    <cfRule type="cellIs" dxfId="72" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:A56">
+    <cfRule type="cellIs" dxfId="66" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:W1048576 A1:W1 B7:E7 P7 AB7:XFD7 C8:E13 C14:D23 D24:D32 C24:C56 Z57:XFD1048576">
-    <cfRule type="cellIs" dxfId="71" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="245" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="64" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F7:F32">
-    <cfRule type="duplicateValues" dxfId="66" priority="1033"/>
-    <cfRule type="cellIs" dxfId="65" priority="51" operator="equal">
+    <cfRule type="duplicateValues" dxfId="60" priority="1033"/>
+    <cfRule type="cellIs" dxfId="59" priority="51" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="64" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33:F50 Q7:Q56 P33:P34 AB33:XFD34 P39:P46 AB39:XFD46 P48:P50 AB48:XFD50">
-    <cfRule type="cellIs" dxfId="63" priority="112" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="112" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33:F50">
-    <cfRule type="duplicateValues" dxfId="62" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="1014"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:F52">
-    <cfRule type="duplicateValues" dxfId="59" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="duplicateValues" dxfId="58" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="57" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="755"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="747"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57:W1048576 W1">
-    <cfRule type="duplicateValues" dxfId="51" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X55">
-    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7">
-    <cfRule type="duplicateValues" dxfId="46" priority="76"/>
-    <cfRule type="cellIs" dxfId="45" priority="75" operator="equal">
+    <cfRule type="duplicateValues" dxfId="40" priority="76"/>
+    <cfRule type="cellIs" dxfId="39" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y8">
-    <cfRule type="duplicateValues" dxfId="44" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y8:Y13 Y22:Y32 Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="40" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y9:Y13 Y24:Y32 Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="39" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y9:Y13 Y24:Y32">
-    <cfRule type="duplicateValues" dxfId="38" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y14">
-    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y20:Y21">
-    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
     <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y22:Y23">
-    <cfRule type="duplicateValues" dxfId="20" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y24:Y32">
-    <cfRule type="duplicateValues" dxfId="15" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:XFD1">
-    <cfRule type="cellIs" dxfId="14" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="231" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA56">
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
+  <conditionalFormatting sqref="AA2:AA56">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8744,7 +8676,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8928,13 +8860,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1019"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9000,15 +8932,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/GEOT/Ontologia_Geotécnica.xlsx
+++ b/Versão5/GEOT/Ontologia_Geotécnica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GEOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82EE8E1-EDE2-4281-956A-19392C781F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387DE0A7-84EB-4C23-B03C-153F0430814B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="396">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1238,9 +1238,6 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1257,6 +1254,12 @@
   </si>
   <si>
     <t>"CTN_PRJ_A"</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>GeoTécnicos</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1775,7 +1778,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1794,12 +1796,12 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="67">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1873,77 +1875,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2415,10 +2351,68 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2889,15 +2883,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="24" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="24"/>
+    <col min="1" max="1" width="9.3046875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="39.15234375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>43</v>
       </c>
@@ -2908,7 +2902,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
@@ -2919,7 +2913,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>47</v>
       </c>
@@ -2930,7 +2924,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>48</v>
       </c>
@@ -2941,7 +2935,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>49</v>
       </c>
@@ -2953,7 +2947,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -2965,7 +2959,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>53</v>
       </c>
@@ -2987,7 +2981,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>54</v>
       </c>
@@ -2998,7 +2992,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>56</v>
       </c>
@@ -3009,7 +3003,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -3020,7 +3014,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
@@ -3031,7 +3025,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
@@ -3042,7 +3036,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
@@ -3053,7 +3047,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
@@ -3064,7 +3058,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
@@ -3075,7 +3069,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -3086,19 +3080,19 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="26">
         <f ca="1">NOW()</f>
-        <v>46216.384563078704</v>
+        <v>46243.522339699077</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>95</v>
       </c>
@@ -3109,7 +3103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>92</v>
       </c>
@@ -3121,7 +3115,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>94</v>
       </c>
@@ -3133,7 +3127,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>66</v>
       </c>
@@ -3144,7 +3138,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>67</v>
       </c>
@@ -3155,7 +3149,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>68</v>
       </c>
@@ -3166,7 +3160,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>69</v>
       </c>
@@ -3177,7 +3171,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
@@ -3197,35 +3191,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
   <dimension ref="A1:AA56"/>
-  <sheetFormatPr defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="64" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="84.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="82" style="57" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9" style="57" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="68.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="57"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="63" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="84.53515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="82" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.53515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.15234375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.3828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.3828125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="68.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -3308,23 +3301,23 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52">
         <v>2</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="58" t="s">
         <v>79</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -3342,19 +3335,19 @@
       <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="60" t="str">
+      <c r="L2" s="59" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
         <v>Gestão</v>
       </c>
-      <c r="M2" s="60" t="str">
+      <c r="M2" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N2" s="60" t="str">
+      <c r="N2" s="59" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
         <v>Contêineres</v>
       </c>
-      <c r="O2" s="60" t="str">
+      <c r="O2" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Contêiner</v>
       </c>
@@ -3362,7 +3355,7 @@
         <v>378</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R2" s="22" t="s">
         <v>9</v>
@@ -3382,7 +3375,7 @@
       <c r="V2" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W2" s="61" t="str">
+      <c r="W2" s="60" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-GEO-",A2)</f>
         <v>Key-GEO-2</v>
       </c>
@@ -3393,30 +3386,30 @@
         <v>9</v>
       </c>
       <c r="Z2" s="22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA2" s="22" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="52">
         <v>3</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="C3" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="58" t="s">
         <v>380</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -3434,19 +3427,19 @@
       <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="60" t="str">
+      <c r="L3" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Gestão</v>
       </c>
-      <c r="M3" s="60" t="str">
+      <c r="M3" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N3" s="60" t="str">
+      <c r="N3" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Contêineres</v>
       </c>
-      <c r="O3" s="60" t="str">
+      <c r="O3" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
@@ -3454,7 +3447,7 @@
         <v>381</v>
       </c>
       <c r="Q3" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R3" s="22" t="s">
         <v>9</v>
@@ -3474,7 +3467,7 @@
       <c r="V3" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W3" s="61" t="str">
+      <c r="W3" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-GEO-3</v>
       </c>
@@ -3492,23 +3485,23 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="52">
         <v>4</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="58" t="s">
         <v>382</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -3526,19 +3519,19 @@
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="60" t="str">
+      <c r="L4" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Gestão</v>
       </c>
-      <c r="M4" s="60" t="str">
+      <c r="M4" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N4" s="60" t="str">
+      <c r="N4" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Contêineres</v>
       </c>
-      <c r="O4" s="60" t="str">
+      <c r="O4" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
@@ -3546,7 +3539,7 @@
         <v>383</v>
       </c>
       <c r="Q4" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R4" s="22" t="s">
         <v>9</v>
@@ -3566,7 +3559,7 @@
       <c r="V4" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W4" s="61" t="str">
+      <c r="W4" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-GEO-4</v>
       </c>
@@ -3584,23 +3577,23 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52">
         <v>5</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="C5" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="58" t="s">
         <v>384</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -3618,19 +3611,19 @@
       <c r="K5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="60" t="str">
+      <c r="L5" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Gestão</v>
       </c>
-      <c r="M5" s="60" t="str">
+      <c r="M5" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N5" s="60" t="str">
+      <c r="N5" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Contêineres</v>
       </c>
-      <c r="O5" s="60" t="str">
+      <c r="O5" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
@@ -3638,7 +3631,7 @@
         <v>385</v>
       </c>
       <c r="Q5" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R5" s="22" t="s">
         <v>9</v>
@@ -3658,7 +3651,7 @@
       <c r="V5" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W5" s="61" t="str">
+      <c r="W5" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-GEO-5</v>
       </c>
@@ -3676,23 +3669,23 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="52">
         <v>6</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="C6" s="58" t="s">
-        <v>379</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="58" t="s">
         <v>386</v>
       </c>
       <c r="G6" s="6" t="s">
@@ -3710,19 +3703,19 @@
       <c r="K6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="60" t="str">
+      <c r="L6" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Gestão</v>
       </c>
-      <c r="M6" s="60" t="str">
+      <c r="M6" s="59" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N6" s="60" t="str">
+      <c r="N6" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Contêineres</v>
       </c>
-      <c r="O6" s="60" t="str">
+      <c r="O6" s="59" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
@@ -3730,7 +3723,7 @@
         <v>387</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>9</v>
@@ -3750,7 +3743,7 @@
       <c r="V6" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W6" s="61" t="str">
+      <c r="W6" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-GEO-6</v>
       </c>
@@ -3768,23 +3761,23 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="52">
         <v>7</v>
       </c>
-      <c r="B7" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C7" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="58" t="s">
         <v>224</v>
       </c>
       <c r="G7" s="6" t="s">
@@ -3802,19 +3795,19 @@
       <c r="K7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="60" t="str">
+      <c r="L7" s="59" t="str">
         <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M7" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M7" s="59" t="str">
         <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N7" s="60" t="str">
+      <c r="N7" s="59" t="str">
         <f t="shared" ref="N7" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Compactação</v>
       </c>
-      <c r="O7" s="60" t="str">
+      <c r="O7" s="59" t="str">
         <f t="shared" ref="O7" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
         <v>Solo Reforçado</v>
       </c>
@@ -3829,7 +3822,7 @@
       </c>
       <c r="S7" s="22" t="str">
         <f t="shared" ref="S7:U7" si="9">SUBSTITUTE(C7, "_", " ")</f>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T7" s="22" t="str">
         <f t="shared" si="9"/>
@@ -3842,14 +3835,14 @@
       <c r="V7" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W7" s="61" t="str">
+      <c r="W7" s="60" t="str">
         <f t="shared" ref="W7:W56" si="10">CONCATENATE("Key-GEO-",A7)</f>
         <v>Key-GEO-7</v>
       </c>
-      <c r="X7" s="63" t="s">
+      <c r="X7" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y7" s="63" t="s">
+      <c r="Y7" s="62" t="s">
         <v>277</v>
       </c>
       <c r="Z7" s="22" t="s">
@@ -3859,23 +3852,23 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="52">
         <v>8</v>
       </c>
-      <c r="B8" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D8" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="58" t="s">
         <v>240</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -3893,19 +3886,19 @@
       <c r="K8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="60" t="str">
+      <c r="L8" s="59" t="str">
         <f t="shared" ref="L8:L56" si="11">CONCATENATE("", C8)</f>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M8" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M8" s="59" t="str">
         <f t="shared" ref="M8:M56" si="12">CONCATENATE("", D8)</f>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N8" s="60" t="str">
+      <c r="N8" s="59" t="str">
         <f t="shared" ref="N8:N56" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Compactação</v>
       </c>
-      <c r="O8" s="60" t="str">
+      <c r="O8" s="59" t="str">
         <f t="shared" ref="O8:O56" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F8),"."," ")," De "," de "))</f>
         <v>Solo Reforçado Dinamicamente</v>
       </c>
@@ -3920,7 +3913,7 @@
       </c>
       <c r="S8" s="22" t="str">
         <f t="shared" ref="S8:S56" si="15">SUBSTITUTE(C8, "_", " ")</f>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T8" s="22" t="str">
         <f t="shared" ref="T8:T56" si="16">SUBSTITUTE(D8, "_", " ")</f>
@@ -3933,14 +3926,14 @@
       <c r="V8" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W8" s="61" t="str">
+      <c r="W8" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-8</v>
       </c>
-      <c r="X8" s="63" t="s">
+      <c r="X8" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y8" s="63" t="s">
+      <c r="Y8" s="62" t="s">
         <v>276</v>
       </c>
       <c r="Z8" s="22" t="s">
@@ -3950,23 +3943,23 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="52">
         <v>9</v>
       </c>
-      <c r="B9" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="58" t="s">
+      <c r="B9" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D9" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="58" t="s">
         <v>241</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -3984,19 +3977,19 @@
       <c r="K9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="60" t="str">
+      <c r="L9" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M9" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M9" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N9" s="60" t="str">
+      <c r="N9" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Compactação</v>
       </c>
-      <c r="O9" s="60" t="str">
+      <c r="O9" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Solo Reforçado Groute</v>
       </c>
@@ -4011,7 +4004,7 @@
       </c>
       <c r="S9" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T9" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4024,14 +4017,14 @@
       <c r="V9" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W9" s="61" t="str">
+      <c r="W9" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-9</v>
       </c>
-      <c r="X9" s="63" t="s">
+      <c r="X9" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y9" s="63" t="s">
+      <c r="Y9" s="62" t="s">
         <v>275</v>
       </c>
       <c r="Z9" s="22" t="s">
@@ -4041,23 +4034,23 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="52">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="58" t="s">
+      <c r="B10" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="58" t="s">
         <v>225</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -4075,19 +4068,19 @@
       <c r="K10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="60" t="str">
+      <c r="L10" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M10" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M10" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N10" s="60" t="str">
+      <c r="N10" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Compactação</v>
       </c>
-      <c r="O10" s="60" t="str">
+      <c r="O10" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Solo Reforçado Substituído</v>
       </c>
@@ -4102,7 +4095,7 @@
       </c>
       <c r="S10" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T10" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4115,14 +4108,14 @@
       <c r="V10" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W10" s="61" t="str">
+      <c r="W10" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-10</v>
       </c>
-      <c r="X10" s="63" t="s">
+      <c r="X10" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y10" s="63" t="s">
+      <c r="Y10" s="62" t="s">
         <v>274</v>
       </c>
       <c r="Z10" s="22" t="s">
@@ -4132,23 +4125,23 @@
         <v>296</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="52">
         <v>11</v>
       </c>
-      <c r="B11" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="58" t="s">
+      <c r="B11" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D11" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="58" t="s">
         <v>242</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -4166,19 +4159,19 @@
       <c r="K11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L11" s="60" t="str">
+      <c r="L11" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M11" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M11" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N11" s="60" t="str">
+      <c r="N11" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Compactação</v>
       </c>
-      <c r="O11" s="60" t="str">
+      <c r="O11" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Solo Reforçado Rolado</v>
       </c>
@@ -4193,7 +4186,7 @@
       </c>
       <c r="S11" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T11" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4206,14 +4199,14 @@
       <c r="V11" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W11" s="61" t="str">
+      <c r="W11" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-11</v>
       </c>
-      <c r="X11" s="63" t="s">
+      <c r="X11" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y11" s="63" t="s">
+      <c r="Y11" s="62" t="s">
         <v>273</v>
       </c>
       <c r="Z11" s="22" t="s">
@@ -4223,23 +4216,23 @@
         <v>297</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="52">
         <v>12</v>
       </c>
-      <c r="B12" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C12" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="58" t="s">
+      <c r="B12" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="58" t="s">
         <v>243</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -4257,19 +4250,19 @@
       <c r="K12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="60" t="str">
+      <c r="L12" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M12" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M12" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N12" s="60" t="str">
+      <c r="N12" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Compactação</v>
       </c>
-      <c r="O12" s="60" t="str">
+      <c r="O12" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Solo Reforçado PréCarregado</v>
       </c>
@@ -4284,7 +4277,7 @@
       </c>
       <c r="S12" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T12" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4297,14 +4290,14 @@
       <c r="V12" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W12" s="61" t="str">
+      <c r="W12" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-12</v>
       </c>
-      <c r="X12" s="63" t="s">
+      <c r="X12" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y12" s="63" t="s">
+      <c r="Y12" s="62" t="s">
         <v>272</v>
       </c>
       <c r="Z12" s="22" t="s">
@@ -4314,23 +4307,23 @@
         <v>298</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="52">
         <v>13</v>
       </c>
-      <c r="B13" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C13" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="58" t="s">
+      <c r="B13" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D13" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="58" t="s">
         <v>244</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -4348,19 +4341,19 @@
       <c r="K13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="60" t="str">
+      <c r="L13" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M13" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M13" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N13" s="60" t="str">
+      <c r="N13" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Compactação</v>
       </c>
-      <c r="O13" s="60" t="str">
+      <c r="O13" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Solo Reforçado Drenado</v>
       </c>
@@ -4375,7 +4368,7 @@
       </c>
       <c r="S13" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T13" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4388,14 +4381,14 @@
       <c r="V13" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W13" s="61" t="str">
+      <c r="W13" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-13</v>
       </c>
-      <c r="X13" s="63" t="s">
+      <c r="X13" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y13" s="63" t="s">
+      <c r="Y13" s="62" t="s">
         <v>271</v>
       </c>
       <c r="Z13" s="22" t="s">
@@ -4405,23 +4398,23 @@
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="52">
         <v>14</v>
       </c>
-      <c r="B14" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C14" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="58" t="s">
+      <c r="B14" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D14" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="58" t="s">
         <v>226</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -4439,19 +4432,19 @@
       <c r="K14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="60" t="str">
+      <c r="L14" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M14" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M14" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N14" s="60" t="str">
+      <c r="N14" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O14" s="60" t="str">
+      <c r="O14" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação</v>
       </c>
@@ -4466,7 +4459,7 @@
       </c>
       <c r="S14" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T14" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4479,14 +4472,14 @@
       <c r="V14" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W14" s="61" t="str">
+      <c r="W14" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-14</v>
       </c>
-      <c r="X14" s="63" t="s">
+      <c r="X14" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y14" s="63" t="s">
+      <c r="Y14" s="62" t="s">
         <v>261</v>
       </c>
       <c r="Z14" s="22" t="s">
@@ -4496,23 +4489,23 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="52">
         <v>15</v>
       </c>
-      <c r="B15" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C15" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="58" t="s">
+      <c r="B15" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D15" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="58" t="s">
         <v>227</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -4530,19 +4523,19 @@
       <c r="K15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="60" t="str">
+      <c r="L15" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M15" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M15" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N15" s="60" t="str">
+      <c r="N15" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O15" s="60" t="str">
+      <c r="O15" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Base</v>
       </c>
@@ -4557,7 +4550,7 @@
       </c>
       <c r="S15" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T15" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4570,14 +4563,14 @@
       <c r="V15" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W15" s="61" t="str">
+      <c r="W15" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-15</v>
       </c>
-      <c r="X15" s="63" t="s">
+      <c r="X15" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y15" s="63" t="s">
+      <c r="Y15" s="62" t="s">
         <v>260</v>
       </c>
       <c r="Z15" s="22" t="s">
@@ -4587,23 +4580,23 @@
         <v>301</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="52">
         <v>16</v>
       </c>
-      <c r="B16" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C16" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="58" t="s">
+      <c r="B16" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D16" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="58" t="s">
         <v>228</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -4621,19 +4614,19 @@
       <c r="K16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="60" t="str">
+      <c r="L16" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M16" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M16" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N16" s="60" t="str">
+      <c r="N16" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O16" s="60" t="str">
+      <c r="O16" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Corte</v>
       </c>
@@ -4648,7 +4641,7 @@
       </c>
       <c r="S16" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T16" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4661,14 +4654,14 @@
       <c r="V16" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W16" s="61" t="str">
+      <c r="W16" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-16</v>
       </c>
-      <c r="X16" s="63" t="s">
+      <c r="X16" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y16" s="63" t="s">
+      <c r="Y16" s="62" t="s">
         <v>259</v>
       </c>
       <c r="Z16" s="22" t="s">
@@ -4678,23 +4671,23 @@
         <v>302</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52">
         <v>17</v>
       </c>
-      <c r="B17" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C17" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="58" t="s">
+      <c r="B17" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D17" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="58" t="s">
         <v>229</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -4712,19 +4705,19 @@
       <c r="K17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L17" s="60" t="str">
+      <c r="L17" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M17" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M17" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N17" s="60" t="str">
+      <c r="N17" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O17" s="60" t="str">
+      <c r="O17" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Dragagem</v>
       </c>
@@ -4739,7 +4732,7 @@
       </c>
       <c r="S17" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T17" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4752,14 +4745,14 @@
       <c r="V17" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W17" s="61" t="str">
+      <c r="W17" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-17</v>
       </c>
-      <c r="X17" s="63" t="s">
+      <c r="X17" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y17" s="63" t="s">
+      <c r="Y17" s="62" t="s">
         <v>258</v>
       </c>
       <c r="Z17" s="22" t="s">
@@ -4769,23 +4762,23 @@
         <v>303</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="52">
         <v>18</v>
       </c>
-      <c r="B18" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" s="58" t="s">
+      <c r="B18" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D18" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="58" t="s">
         <v>234</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -4803,19 +4796,19 @@
       <c r="K18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L18" s="60" t="str">
+      <c r="L18" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M18" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M18" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N18" s="60" t="str">
+      <c r="N18" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O18" s="60" t="str">
+      <c r="O18" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Terreno</v>
       </c>
@@ -4830,7 +4823,7 @@
       </c>
       <c r="S18" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T18" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4843,14 +4836,14 @@
       <c r="V18" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W18" s="61" t="str">
+      <c r="W18" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-18</v>
       </c>
-      <c r="X18" s="63" t="s">
+      <c r="X18" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y18" s="63" t="s">
+      <c r="Y18" s="62" t="s">
         <v>257</v>
       </c>
       <c r="Z18" s="22" t="s">
@@ -4860,23 +4853,23 @@
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="52">
         <v>19</v>
       </c>
-      <c r="B19" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C19" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="58" t="s">
+      <c r="B19" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D19" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="58" t="s">
         <v>233</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -4894,19 +4887,19 @@
       <c r="K19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L19" s="60" t="str">
+      <c r="L19" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M19" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M19" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N19" s="60" t="str">
+      <c r="N19" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O19" s="60" t="str">
+      <c r="O19" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação SobreEscavação</v>
       </c>
@@ -4921,7 +4914,7 @@
       </c>
       <c r="S19" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T19" s="22" t="str">
         <f t="shared" si="16"/>
@@ -4934,14 +4927,14 @@
       <c r="V19" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W19" s="61" t="str">
+      <c r="W19" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-19</v>
       </c>
-      <c r="X19" s="63" t="s">
+      <c r="X19" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y19" s="63" t="s">
+      <c r="Y19" s="62" t="s">
         <v>256</v>
       </c>
       <c r="Z19" s="22" t="s">
@@ -4951,23 +4944,23 @@
         <v>305</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="52">
         <v>20</v>
       </c>
-      <c r="B20" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C20" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="58" t="s">
+      <c r="B20" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D20" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="58" t="s">
         <v>230</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -4985,19 +4978,19 @@
       <c r="K20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L20" s="60" t="str">
+      <c r="L20" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M20" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M20" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N20" s="60" t="str">
+      <c r="N20" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O20" s="60" t="str">
+      <c r="O20" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Fresagem</v>
       </c>
@@ -5012,7 +5005,7 @@
       </c>
       <c r="S20" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T20" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5025,14 +5018,14 @@
       <c r="V20" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W20" s="61" t="str">
+      <c r="W20" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-20</v>
       </c>
-      <c r="X20" s="63" t="s">
+      <c r="X20" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y20" s="63" t="s">
+      <c r="Y20" s="62" t="s">
         <v>255</v>
       </c>
       <c r="Z20" s="22" t="s">
@@ -5042,23 +5035,23 @@
         <v>306</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="52">
         <v>21</v>
       </c>
-      <c r="B21" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C21" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" s="58" t="s">
+      <c r="B21" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D21" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="58" t="s">
         <v>251</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -5076,19 +5069,19 @@
       <c r="K21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L21" s="60" t="str">
+      <c r="L21" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M21" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M21" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N21" s="60" t="str">
+      <c r="N21" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O21" s="60" t="str">
+      <c r="O21" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Banqueta</v>
       </c>
@@ -5103,7 +5096,7 @@
       </c>
       <c r="S21" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T21" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5116,14 +5109,14 @@
       <c r="V21" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W21" s="61" t="str">
+      <c r="W21" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-21</v>
       </c>
-      <c r="X21" s="63" t="s">
+      <c r="X21" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y21" s="63" t="s">
+      <c r="Y21" s="62" t="s">
         <v>254</v>
       </c>
       <c r="Z21" s="22" t="s">
@@ -5133,23 +5126,23 @@
         <v>307</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="52">
         <v>22</v>
       </c>
-      <c r="B22" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C22" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="58" t="s">
+      <c r="B22" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D22" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="58" t="s">
         <v>231</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -5167,19 +5160,19 @@
       <c r="K22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L22" s="60" t="str">
+      <c r="L22" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M22" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M22" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N22" s="60" t="str">
+      <c r="N22" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O22" s="60" t="str">
+      <c r="O22" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Remoção</v>
       </c>
@@ -5194,7 +5187,7 @@
       </c>
       <c r="S22" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T22" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5207,14 +5200,14 @@
       <c r="V22" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W22" s="61" t="str">
+      <c r="W22" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-22</v>
       </c>
-      <c r="X22" s="63" t="s">
+      <c r="X22" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y22" s="63" t="s">
+      <c r="Y22" s="62" t="s">
         <v>253</v>
       </c>
       <c r="Z22" s="22" t="s">
@@ -5224,23 +5217,23 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="52">
         <v>23</v>
       </c>
-      <c r="B23" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C23" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="58" t="s">
+      <c r="B23" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="57" t="s">
         <v>288</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="58" t="s">
         <v>232</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -5258,19 +5251,19 @@
       <c r="K23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L23" s="60" t="str">
+      <c r="L23" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M23" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M23" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N23" s="60" t="str">
+      <c r="N23" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Escavações</v>
       </c>
-      <c r="O23" s="60" t="str">
+      <c r="O23" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Escavação Trincheira</v>
       </c>
@@ -5285,7 +5278,7 @@
       </c>
       <c r="S23" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T23" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5298,14 +5291,14 @@
       <c r="V23" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W23" s="61" t="str">
+      <c r="W23" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-23</v>
       </c>
-      <c r="X23" s="63" t="s">
+      <c r="X23" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y23" s="63" t="s">
+      <c r="Y23" s="62" t="s">
         <v>252</v>
       </c>
       <c r="Z23" s="22" t="s">
@@ -5315,23 +5308,23 @@
         <v>309</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="52">
         <v>24</v>
       </c>
-      <c r="B24" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C24" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="58" t="s">
+      <c r="B24" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D24" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="58" t="s">
         <v>247</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -5349,19 +5342,19 @@
       <c r="K24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L24" s="60" t="str">
+      <c r="L24" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M24" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M24" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N24" s="60" t="str">
+      <c r="N24" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O24" s="60" t="str">
+      <c r="O24" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Terrapleno</v>
       </c>
@@ -5376,7 +5369,7 @@
       </c>
       <c r="S24" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T24" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5389,14 +5382,14 @@
       <c r="V24" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W24" s="61" t="str">
+      <c r="W24" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-24</v>
       </c>
-      <c r="X24" s="63" t="s">
+      <c r="X24" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y24" s="63" t="s">
+      <c r="Y24" s="62" t="s">
         <v>270</v>
       </c>
       <c r="Z24" s="22" t="s">
@@ -5406,23 +5399,23 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="52">
         <v>25</v>
       </c>
-      <c r="B25" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C25" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="58" t="s">
+      <c r="B25" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D25" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E25" s="58" t="s">
+      <c r="E25" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="58" t="s">
         <v>248</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -5440,19 +5433,19 @@
       <c r="K25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="60" t="str">
+      <c r="L25" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M25" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M25" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N25" s="60" t="str">
+      <c r="N25" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O25" s="60" t="str">
+      <c r="O25" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Terrapleno</v>
       </c>
@@ -5467,7 +5460,7 @@
       </c>
       <c r="S25" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T25" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5480,14 +5473,14 @@
       <c r="V25" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W25" s="61" t="str">
+      <c r="W25" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-25</v>
       </c>
-      <c r="X25" s="63" t="s">
+      <c r="X25" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y25" s="63" t="s">
+      <c r="Y25" s="62" t="s">
         <v>269</v>
       </c>
       <c r="Z25" s="22" t="s">
@@ -5497,23 +5490,23 @@
         <v>310</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="52">
         <v>26</v>
       </c>
-      <c r="B26" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="58" t="s">
+      <c r="B26" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D26" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E26" s="58" t="s">
+      <c r="E26" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="58" t="s">
         <v>249</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -5531,19 +5524,19 @@
       <c r="K26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L26" s="60" t="str">
+      <c r="L26" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M26" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M26" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N26" s="60" t="str">
+      <c r="N26" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O26" s="60" t="str">
+      <c r="O26" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Reenchimento</v>
       </c>
@@ -5558,7 +5551,7 @@
       </c>
       <c r="S26" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T26" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5571,14 +5564,14 @@
       <c r="V26" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W26" s="61" t="str">
+      <c r="W26" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-26</v>
       </c>
-      <c r="X26" s="63" t="s">
+      <c r="X26" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y26" s="63" t="s">
+      <c r="Y26" s="62" t="s">
         <v>268</v>
       </c>
       <c r="Z26" s="22" t="s">
@@ -5588,23 +5581,23 @@
         <v>311</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="52">
         <v>27</v>
       </c>
-      <c r="B27" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="58" t="s">
+      <c r="B27" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D27" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="58" t="s">
         <v>235</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -5622,19 +5615,19 @@
       <c r="K27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L27" s="60" t="str">
+      <c r="L27" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M27" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M27" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N27" s="60" t="str">
+      <c r="N27" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O27" s="60" t="str">
+      <c r="O27" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Contrapeso</v>
       </c>
@@ -5649,7 +5642,7 @@
       </c>
       <c r="S27" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T27" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5662,14 +5655,14 @@
       <c r="V27" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W27" s="61" t="str">
+      <c r="W27" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-27</v>
       </c>
-      <c r="X27" s="63" t="s">
+      <c r="X27" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y27" s="63" t="s">
+      <c r="Y27" s="62" t="s">
         <v>267</v>
       </c>
       <c r="Z27" s="22" t="s">
@@ -5679,23 +5672,23 @@
         <v>312</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="52">
         <v>28</v>
       </c>
-      <c r="B28" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="58" t="s">
+      <c r="B28" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D28" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="E28" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="58" t="s">
         <v>236</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -5713,19 +5706,19 @@
       <c r="K28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L28" s="60" t="str">
+      <c r="L28" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M28" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M28" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N28" s="60" t="str">
+      <c r="N28" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O28" s="60" t="str">
+      <c r="O28" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Preenchimento</v>
       </c>
@@ -5740,7 +5733,7 @@
       </c>
       <c r="S28" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T28" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5753,14 +5746,14 @@
       <c r="V28" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W28" s="61" t="str">
+      <c r="W28" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-28</v>
       </c>
-      <c r="X28" s="63" t="s">
+      <c r="X28" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y28" s="63" t="s">
+      <c r="Y28" s="62" t="s">
         <v>266</v>
       </c>
       <c r="Z28" s="22" t="s">
@@ -5770,23 +5763,23 @@
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="52">
         <v>29</v>
       </c>
-      <c r="B29" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="B29" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D29" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="58" t="s">
         <v>237</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -5804,19 +5797,19 @@
       <c r="K29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="60" t="str">
+      <c r="L29" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M29" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M29" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N29" s="60" t="str">
+      <c r="N29" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O29" s="60" t="str">
+      <c r="O29" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Inclinado</v>
       </c>
@@ -5831,7 +5824,7 @@
       </c>
       <c r="S29" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T29" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5844,14 +5837,14 @@
       <c r="V29" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W29" s="61" t="str">
+      <c r="W29" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-29</v>
       </c>
-      <c r="X29" s="63" t="s">
+      <c r="X29" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y29" s="63" t="s">
+      <c r="Y29" s="62" t="s">
         <v>265</v>
       </c>
       <c r="Z29" s="22" t="s">
@@ -5861,23 +5854,23 @@
         <v>314</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="52">
         <v>30</v>
       </c>
-      <c r="B30" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="58" t="s">
+      <c r="B30" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D30" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="58" t="s">
         <v>250</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -5895,19 +5888,19 @@
       <c r="K30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L30" s="60" t="str">
+      <c r="L30" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M30" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M30" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N30" s="60" t="str">
+      <c r="N30" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O30" s="60" t="str">
+      <c r="O30" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Subterrâneo</v>
       </c>
@@ -5922,7 +5915,7 @@
       </c>
       <c r="S30" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T30" s="22" t="str">
         <f t="shared" si="16"/>
@@ -5935,14 +5928,14 @@
       <c r="V30" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W30" s="61" t="str">
+      <c r="W30" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-30</v>
       </c>
-      <c r="X30" s="63" t="s">
+      <c r="X30" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y30" s="63" t="s">
+      <c r="Y30" s="62" t="s">
         <v>264</v>
       </c>
       <c r="Z30" s="22" t="s">
@@ -5952,23 +5945,23 @@
         <v>315</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="52">
         <v>31</v>
       </c>
-      <c r="B31" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="B31" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C31" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E31" s="58" t="s">
+      <c r="E31" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="58" t="s">
         <v>238</v>
       </c>
       <c r="G31" s="6" t="s">
@@ -5986,19 +5979,19 @@
       <c r="K31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L31" s="60" t="str">
+      <c r="L31" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M31" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M31" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N31" s="60" t="str">
+      <c r="N31" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O31" s="60" t="str">
+      <c r="O31" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Camada</v>
       </c>
@@ -6013,7 +6006,7 @@
       </c>
       <c r="S31" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T31" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6026,14 +6019,14 @@
       <c r="V31" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W31" s="61" t="str">
+      <c r="W31" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-31</v>
       </c>
-      <c r="X31" s="63" t="s">
+      <c r="X31" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y31" s="63" t="s">
+      <c r="Y31" s="62" t="s">
         <v>263</v>
       </c>
       <c r="Z31" s="22" t="s">
@@ -6043,23 +6036,23 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="52">
         <v>32</v>
       </c>
-      <c r="B32" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C32" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="B32" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="58" t="s">
         <v>239</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -6077,19 +6070,19 @@
       <c r="K32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L32" s="60" t="str">
+      <c r="L32" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M32" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M32" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N32" s="60" t="str">
+      <c r="N32" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O32" s="60" t="str">
+      <c r="O32" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Aterro Transição</v>
       </c>
@@ -6104,7 +6097,7 @@
       </c>
       <c r="S32" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T32" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6117,14 +6110,14 @@
       <c r="V32" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W32" s="61" t="str">
+      <c r="W32" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-32</v>
       </c>
-      <c r="X32" s="63" t="s">
+      <c r="X32" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y32" s="63" t="s">
+      <c r="Y32" s="62" t="s">
         <v>262</v>
       </c>
       <c r="Z32" s="22" t="s">
@@ -6134,17 +6127,17 @@
         <v>317</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="52">
         <v>33</v>
       </c>
-      <c r="B33" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" s="58" t="s">
+      <c r="B33" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C33" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D33" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E33" s="45" t="s">
@@ -6168,19 +6161,19 @@
       <c r="K33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L33" s="60" t="str">
+      <c r="L33" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M33" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M33" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N33" s="60" t="str">
+      <c r="N33" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O33" s="60" t="str">
+      <c r="O33" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Interno</v>
       </c>
@@ -6195,7 +6188,7 @@
       </c>
       <c r="S33" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T33" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6208,7 +6201,7 @@
       <c r="V33" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W33" s="61" t="str">
+      <c r="W33" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-33</v>
       </c>
@@ -6225,17 +6218,17 @@
         <v>318</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="52">
         <v>34</v>
       </c>
-      <c r="B34" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C34" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="58" t="s">
+      <c r="B34" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C34" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D34" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E34" s="45" t="s">
@@ -6259,19 +6252,19 @@
       <c r="K34" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L34" s="60" t="str">
+      <c r="L34" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M34" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M34" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N34" s="60" t="str">
+      <c r="N34" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O34" s="60" t="str">
+      <c r="O34" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Perimetral</v>
       </c>
@@ -6286,7 +6279,7 @@
       </c>
       <c r="S34" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T34" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6299,7 +6292,7 @@
       <c r="V34" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W34" s="61" t="str">
+      <c r="W34" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-34</v>
       </c>
@@ -6316,17 +6309,17 @@
         <v>319</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="52">
         <v>35</v>
       </c>
-      <c r="B35" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="58" t="s">
+      <c r="B35" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C35" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D35" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E35" s="45" t="s">
@@ -6350,19 +6343,19 @@
       <c r="K35" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L35" s="60" t="str">
+      <c r="L35" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M35" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M35" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N35" s="60" t="str">
+      <c r="N35" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O35" s="60" t="str">
+      <c r="O35" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Região</v>
       </c>
@@ -6377,7 +6370,7 @@
       </c>
       <c r="S35" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T35" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6390,7 +6383,7 @@
       <c r="V35" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W35" s="61" t="str">
+      <c r="W35" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-35</v>
       </c>
@@ -6407,17 +6400,17 @@
         <v>320</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="52">
         <v>36</v>
       </c>
-      <c r="B36" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C36" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D36" s="58" t="s">
+      <c r="B36" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C36" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D36" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E36" s="45" t="s">
@@ -6441,19 +6434,19 @@
       <c r="K36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L36" s="60" t="str">
+      <c r="L36" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M36" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M36" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N36" s="60" t="str">
+      <c r="N36" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O36" s="60" t="str">
+      <c r="O36" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Superfície</v>
       </c>
@@ -6468,7 +6461,7 @@
       </c>
       <c r="S36" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T36" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6481,7 +6474,7 @@
       <c r="V36" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W36" s="61" t="str">
+      <c r="W36" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-36</v>
       </c>
@@ -6498,20 +6491,20 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="52">
         <v>37</v>
       </c>
-      <c r="B37" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C37" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D37" s="58" t="s">
+      <c r="B37" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" s="57" t="s">
         <v>278</v>
       </c>
-      <c r="E37" s="58" t="s">
+      <c r="E37" s="57" t="s">
         <v>173</v>
       </c>
       <c r="F37" s="45" t="s">
@@ -6532,19 +6525,19 @@
       <c r="K37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L37" s="60" t="str">
+      <c r="L37" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M37" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M37" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N37" s="60" t="str">
+      <c r="N37" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Sondagens</v>
       </c>
-      <c r="O37" s="60" t="str">
+      <c r="O37" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Sondagem</v>
       </c>
@@ -6559,7 +6552,7 @@
       </c>
       <c r="S37" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T37" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6572,14 +6565,14 @@
       <c r="V37" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W37" s="61" t="str">
+      <c r="W37" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-37</v>
       </c>
       <c r="X37" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="Y37" s="63" t="s">
+      <c r="Y37" s="62" t="s">
         <v>219</v>
       </c>
       <c r="Z37" s="22" t="s">
@@ -6589,20 +6582,20 @@
         <v>322</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="52">
         <v>38</v>
       </c>
-      <c r="B38" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C38" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="58" t="s">
+      <c r="B38" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C38" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D38" s="57" t="s">
         <v>278</v>
       </c>
-      <c r="E38" s="58" t="s">
+      <c r="E38" s="57" t="s">
         <v>173</v>
       </c>
       <c r="F38" s="45" t="s">
@@ -6623,19 +6616,19 @@
       <c r="K38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L38" s="60" t="str">
+      <c r="L38" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M38" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M38" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N38" s="60" t="str">
+      <c r="N38" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Sondagens</v>
       </c>
-      <c r="O38" s="60" t="str">
+      <c r="O38" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Ponto Sondagem Definido</v>
       </c>
@@ -6650,7 +6643,7 @@
       </c>
       <c r="S38" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T38" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6663,14 +6656,14 @@
       <c r="V38" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W38" s="61" t="str">
+      <c r="W38" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-38</v>
       </c>
       <c r="X38" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="Y38" s="63" t="s">
+      <c r="Y38" s="62" t="s">
         <v>220</v>
       </c>
       <c r="Z38" s="22" t="s">
@@ -6680,17 +6673,17 @@
         <v>323</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="52">
         <v>39</v>
       </c>
-      <c r="B39" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C39" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D39" s="58" t="s">
+      <c r="B39" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D39" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E39" s="45" t="s">
@@ -6714,19 +6707,19 @@
       <c r="K39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L39" s="60" t="str">
+      <c r="L39" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M39" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M39" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N39" s="60" t="str">
+      <c r="N39" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O39" s="60" t="str">
+      <c r="O39" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida</v>
       </c>
@@ -6741,7 +6734,7 @@
       </c>
       <c r="S39" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T39" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6754,7 +6747,7 @@
       <c r="V39" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W39" s="61" t="str">
+      <c r="W39" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-39</v>
       </c>
@@ -6771,17 +6764,17 @@
         <v>324</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="52">
         <v>40</v>
       </c>
-      <c r="B40" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C40" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="58" t="s">
+      <c r="B40" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D40" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E40" s="45" t="s">
@@ -6805,19 +6798,19 @@
       <c r="K40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L40" s="60" t="str">
+      <c r="L40" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M40" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M40" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N40" s="60" t="str">
+      <c r="N40" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O40" s="60" t="str">
+      <c r="O40" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Malha</v>
       </c>
@@ -6832,7 +6825,7 @@
       </c>
       <c r="S40" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T40" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6845,7 +6838,7 @@
       <c r="V40" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W40" s="61" t="str">
+      <c r="W40" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-40</v>
       </c>
@@ -6862,17 +6855,17 @@
         <v>325</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="52">
         <v>41</v>
       </c>
-      <c r="B41" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C41" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="58" t="s">
+      <c r="B41" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D41" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E41" s="45" t="s">
@@ -6896,19 +6889,19 @@
       <c r="K41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L41" s="60" t="str">
+      <c r="L41" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M41" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M41" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N41" s="60" t="str">
+      <c r="N41" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O41" s="60" t="str">
+      <c r="O41" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Núcleo</v>
       </c>
@@ -6923,7 +6916,7 @@
       </c>
       <c r="S41" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T41" s="22" t="str">
         <f t="shared" si="16"/>
@@ -6936,7 +6929,7 @@
       <c r="V41" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W41" s="61" t="str">
+      <c r="W41" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-41</v>
       </c>
@@ -6953,17 +6946,17 @@
         <v>326</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="52">
         <v>42</v>
       </c>
-      <c r="B42" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C42" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" s="58" t="s">
+      <c r="B42" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D42" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E42" s="45" t="s">
@@ -6987,19 +6980,19 @@
       <c r="K42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L42" s="60" t="str">
+      <c r="L42" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M42" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M42" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N42" s="60" t="str">
+      <c r="N42" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O42" s="60" t="str">
+      <c r="O42" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Substrato</v>
       </c>
@@ -7014,7 +7007,7 @@
       </c>
       <c r="S42" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T42" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7027,7 +7020,7 @@
       <c r="V42" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W42" s="61" t="str">
+      <c r="W42" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-42</v>
       </c>
@@ -7044,17 +7037,17 @@
         <v>327</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="52">
         <v>43</v>
       </c>
-      <c r="B43" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C43" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D43" s="58" t="s">
+      <c r="B43" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D43" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E43" s="45" t="s">
@@ -7078,19 +7071,19 @@
       <c r="K43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L43" s="60" t="str">
+      <c r="L43" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M43" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M43" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N43" s="60" t="str">
+      <c r="N43" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O43" s="60" t="str">
+      <c r="O43" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Membrana</v>
       </c>
@@ -7105,7 +7098,7 @@
       </c>
       <c r="S43" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T43" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7118,7 +7111,7 @@
       <c r="V43" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W43" s="61" t="str">
+      <c r="W43" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-43</v>
       </c>
@@ -7135,17 +7128,17 @@
         <v>328</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="52">
         <v>44</v>
       </c>
-      <c r="B44" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C44" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="58" t="s">
+      <c r="B44" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C44" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D44" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E44" s="45" t="s">
@@ -7169,19 +7162,19 @@
       <c r="K44" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="60" t="str">
+      <c r="L44" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M44" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M44" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N44" s="60" t="str">
+      <c r="N44" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O44" s="60" t="str">
+      <c r="O44" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Isolamento</v>
       </c>
@@ -7196,7 +7189,7 @@
       </c>
       <c r="S44" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T44" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7209,7 +7202,7 @@
       <c r="V44" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W44" s="61" t="str">
+      <c r="W44" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-44</v>
       </c>
@@ -7226,17 +7219,17 @@
         <v>329</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="52">
         <v>45</v>
       </c>
-      <c r="B45" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C45" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D45" s="58" t="s">
+      <c r="B45" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C45" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D45" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E45" s="45" t="s">
@@ -7260,19 +7253,19 @@
       <c r="K45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L45" s="60" t="str">
+      <c r="L45" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M45" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M45" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N45" s="60" t="str">
+      <c r="N45" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O45" s="60" t="str">
+      <c r="O45" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Superfície</v>
       </c>
@@ -7287,7 +7280,7 @@
       </c>
       <c r="S45" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T45" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7300,7 +7293,7 @@
       <c r="V45" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W45" s="61" t="str">
+      <c r="W45" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-45</v>
       </c>
@@ -7317,17 +7310,17 @@
         <v>330</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="52">
         <v>46</v>
       </c>
-      <c r="B46" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C46" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="58" t="s">
+      <c r="B46" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C46" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D46" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E46" s="45" t="s">
@@ -7351,19 +7344,19 @@
       <c r="K46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L46" s="60" t="str">
+      <c r="L46" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M46" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M46" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N46" s="60" t="str">
+      <c r="N46" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O46" s="60" t="str">
+      <c r="O46" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Agua</v>
       </c>
@@ -7378,7 +7371,7 @@
       </c>
       <c r="S46" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T46" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7391,7 +7384,7 @@
       <c r="V46" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W46" s="61" t="str">
+      <c r="W46" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-46</v>
       </c>
@@ -7408,17 +7401,17 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="52">
         <v>47</v>
       </c>
-      <c r="B47" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C47" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D47" s="58" t="s">
+      <c r="B47" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C47" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D47" s="57" t="s">
         <v>278</v>
       </c>
       <c r="E47" s="45" t="s">
@@ -7442,19 +7435,19 @@
       <c r="K47" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L47" s="60" t="str">
+      <c r="L47" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M47" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M47" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N47" s="60" t="str">
+      <c r="N47" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Topografia</v>
       </c>
-      <c r="O47" s="60" t="str">
+      <c r="O47" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Topografia Sólida Vazio</v>
       </c>
@@ -7469,7 +7462,7 @@
       </c>
       <c r="S47" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T47" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7482,14 +7475,14 @@
       <c r="V47" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W47" s="61" t="str">
+      <c r="W47" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-47</v>
       </c>
-      <c r="X47" s="63" t="s">
+      <c r="X47" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="Y47" s="63" t="s">
+      <c r="Y47" s="62" t="s">
         <v>199</v>
       </c>
       <c r="Z47" s="22" t="s">
@@ -7499,17 +7492,17 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="52">
         <v>48</v>
       </c>
-      <c r="B48" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C48" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="58" t="s">
+      <c r="B48" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C48" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D48" s="57" t="s">
         <v>185</v>
       </c>
       <c r="E48" s="45" t="s">
@@ -7533,19 +7526,19 @@
       <c r="K48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L48" s="60" t="str">
+      <c r="L48" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M48" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M48" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N48" s="60" t="str">
+      <c r="N48" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O48" s="60" t="str">
+      <c r="O48" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Curva de 10</v>
       </c>
@@ -7560,7 +7553,7 @@
       </c>
       <c r="S48" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T48" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7573,7 +7566,7 @@
       <c r="V48" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W48" s="61" t="str">
+      <c r="W48" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-48</v>
       </c>
@@ -7590,17 +7583,17 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="52">
         <v>49</v>
       </c>
-      <c r="B49" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C49" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D49" s="58" t="s">
+      <c r="B49" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C49" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D49" s="57" t="s">
         <v>185</v>
       </c>
       <c r="E49" s="45" t="s">
@@ -7624,19 +7617,19 @@
       <c r="K49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L49" s="60" t="str">
+      <c r="L49" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M49" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M49" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N49" s="60" t="str">
+      <c r="N49" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O49" s="60" t="str">
+      <c r="O49" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Curva de 05</v>
       </c>
@@ -7651,7 +7644,7 @@
       </c>
       <c r="S49" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T49" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7664,7 +7657,7 @@
       <c r="V49" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W49" s="61" t="str">
+      <c r="W49" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-49</v>
       </c>
@@ -7681,17 +7674,17 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="52">
         <v>50</v>
       </c>
-      <c r="B50" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C50" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D50" s="58" t="s">
+      <c r="B50" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C50" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D50" s="57" t="s">
         <v>185</v>
       </c>
       <c r="E50" s="45" t="s">
@@ -7715,19 +7708,19 @@
       <c r="K50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L50" s="60" t="str">
+      <c r="L50" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M50" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M50" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N50" s="60" t="str">
+      <c r="N50" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O50" s="60" t="str">
+      <c r="O50" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Curva de 01</v>
       </c>
@@ -7742,7 +7735,7 @@
       </c>
       <c r="S50" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T50" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7755,7 +7748,7 @@
       <c r="V50" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W50" s="61" t="str">
+      <c r="W50" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-50</v>
       </c>
@@ -7772,23 +7765,23 @@
         <v>335</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="52">
         <v>51</v>
       </c>
-      <c r="B51" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C51" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D51" s="58" t="s">
+      <c r="B51" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C51" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D51" s="57" t="s">
         <v>279</v>
       </c>
-      <c r="E51" s="58" t="s">
+      <c r="E51" s="57" t="s">
         <v>280</v>
       </c>
-      <c r="F51" s="58" t="s">
+      <c r="F51" s="57" t="s">
         <v>215</v>
       </c>
       <c r="G51" s="6" t="s">
@@ -7806,19 +7799,19 @@
       <c r="K51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L51" s="60" t="str">
+      <c r="L51" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M51" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M51" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="N51" s="60" t="str">
+      <c r="N51" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Loteamento</v>
       </c>
-      <c r="O51" s="60" t="str">
+      <c r="O51" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Divisa</v>
       </c>
@@ -7833,7 +7826,7 @@
       </c>
       <c r="S51" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T51" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7846,7 +7839,7 @@
       <c r="V51" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W51" s="61" t="str">
+      <c r="W51" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-51</v>
       </c>
@@ -7863,23 +7856,23 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="52">
         <v>52</v>
       </c>
-      <c r="B52" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C52" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D52" s="58" t="s">
+      <c r="B52" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C52" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D52" s="57" t="s">
         <v>279</v>
       </c>
-      <c r="E52" s="58" t="s">
+      <c r="E52" s="57" t="s">
         <v>280</v>
       </c>
-      <c r="F52" s="58" t="s">
+      <c r="F52" s="57" t="s">
         <v>216</v>
       </c>
       <c r="G52" s="6" t="s">
@@ -7897,19 +7890,19 @@
       <c r="K52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L52" s="60" t="str">
+      <c r="L52" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M52" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M52" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="N52" s="60" t="str">
+      <c r="N52" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Loteamento</v>
       </c>
-      <c r="O52" s="60" t="str">
+      <c r="O52" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Divisa Segmento</v>
       </c>
@@ -7924,7 +7917,7 @@
       </c>
       <c r="S52" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T52" s="22" t="str">
         <f t="shared" si="16"/>
@@ -7937,7 +7930,7 @@
       <c r="V52" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W52" s="61" t="str">
+      <c r="W52" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-52</v>
       </c>
@@ -7954,23 +7947,23 @@
         <v>336</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="52">
         <v>53</v>
       </c>
-      <c r="B53" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C53" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D53" s="58" t="s">
+      <c r="B53" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C53" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D53" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="E53" s="58" t="s">
+      <c r="E53" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="F53" s="59" t="s">
+      <c r="F53" s="58" t="s">
         <v>281</v>
       </c>
       <c r="G53" s="6" t="s">
@@ -7988,19 +7981,19 @@
       <c r="K53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L53" s="60" t="str">
+      <c r="L53" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M53" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M53" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N53" s="60" t="str">
+      <c r="N53" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O53" s="60" t="str">
+      <c r="O53" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Paisagístico</v>
       </c>
@@ -8015,7 +8008,7 @@
       </c>
       <c r="S53" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T53" s="22" t="str">
         <f t="shared" si="16"/>
@@ -8028,14 +8021,14 @@
       <c r="V53" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W53" s="61" t="str">
+      <c r="W53" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-53</v>
       </c>
-      <c r="X53" s="63" t="s">
+      <c r="X53" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="Y53" s="63" t="s">
+      <c r="Y53" s="62" t="s">
         <v>174</v>
       </c>
       <c r="Z53" s="22" t="s">
@@ -8045,23 +8038,23 @@
         <v>337</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="52">
         <v>54</v>
       </c>
-      <c r="B54" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C54" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D54" s="58" t="s">
+      <c r="B54" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C54" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D54" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="58" t="s">
+      <c r="E54" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="F54" s="59" t="s">
+      <c r="F54" s="58" t="s">
         <v>287</v>
       </c>
       <c r="G54" s="6" t="s">
@@ -8079,19 +8072,19 @@
       <c r="K54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L54" s="60" t="str">
+      <c r="L54" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M54" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M54" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N54" s="60" t="str">
+      <c r="N54" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O54" s="60" t="str">
+      <c r="O54" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Pavimentação</v>
       </c>
@@ -8106,7 +8099,7 @@
       </c>
       <c r="S54" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T54" s="22" t="str">
         <f t="shared" si="16"/>
@@ -8119,14 +8112,14 @@
       <c r="V54" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W54" s="61" t="str">
+      <c r="W54" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-54</v>
       </c>
-      <c r="X54" s="63" t="s">
+      <c r="X54" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="Y54" s="63" t="s">
+      <c r="Y54" s="62" t="s">
         <v>193</v>
       </c>
       <c r="Z54" s="22" t="s">
@@ -8136,23 +8129,23 @@
         <v>338</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="52">
         <v>55</v>
       </c>
-      <c r="B55" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C55" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D55" s="58" t="s">
+      <c r="B55" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C55" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D55" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="E55" s="58" t="s">
+      <c r="E55" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="F55" s="58" t="s">
+      <c r="F55" s="57" t="s">
         <v>82</v>
       </c>
       <c r="G55" s="6" t="s">
@@ -8170,19 +8163,19 @@
       <c r="K55" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L55" s="60" t="str">
+      <c r="L55" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M55" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M55" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N55" s="60" t="str">
+      <c r="N55" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O55" s="60" t="str">
+      <c r="O55" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Estacionamento</v>
       </c>
@@ -8197,7 +8190,7 @@
       </c>
       <c r="S55" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T55" s="22" t="str">
         <f t="shared" si="16"/>
@@ -8210,14 +8203,14 @@
       <c r="V55" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W55" s="61" t="str">
+      <c r="W55" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-55</v>
       </c>
       <c r="X55" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="Y55" s="63" t="s">
+      <c r="Y55" s="62" t="s">
         <v>282</v>
       </c>
       <c r="Z55" s="22" t="s">
@@ -8227,23 +8220,23 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="52">
         <v>56</v>
       </c>
-      <c r="B56" s="58" t="s">
-        <v>388</v>
-      </c>
-      <c r="C56" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D56" s="58" t="s">
+      <c r="B56" s="57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="D56" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="E56" s="58" t="s">
+      <c r="E56" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="F56" s="59" t="s">
+      <c r="F56" s="58" t="s">
         <v>148</v>
       </c>
       <c r="G56" s="6" t="s">
@@ -8261,19 +8254,19 @@
       <c r="K56" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L56" s="60" t="str">
+      <c r="L56" s="59" t="str">
         <f t="shared" si="11"/>
-        <v>GeoTécnico</v>
-      </c>
-      <c r="M56" s="60" t="str">
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="M56" s="59" t="str">
         <f t="shared" si="12"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N56" s="60" t="str">
+      <c r="N56" s="59" t="str">
         <f t="shared" si="13"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O56" s="60" t="str">
+      <c r="O56" s="59" t="str">
         <f t="shared" si="14"/>
         <v>Vegetação</v>
       </c>
@@ -8288,7 +8281,7 @@
       </c>
       <c r="S56" s="22" t="str">
         <f t="shared" si="15"/>
-        <v>GeoTécnico</v>
+        <v>GeoTécnicos</v>
       </c>
       <c r="T56" s="22" t="str">
         <f t="shared" si="16"/>
@@ -8301,14 +8294,14 @@
       <c r="V56" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="W56" s="61" t="str">
+      <c r="W56" s="60" t="str">
         <f t="shared" si="10"/>
         <v>Key-GEO-56</v>
       </c>
-      <c r="X56" s="63" t="s">
+      <c r="X56" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="Y56" s="63" t="s">
+      <c r="Y56" s="62" t="s">
         <v>194</v>
       </c>
       <c r="Z56" s="22" t="s">
@@ -8323,131 +8316,126 @@
     <sortCondition ref="E1:E809"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A57:W1048576 A1:W1 P7 AB7:XFD7 C7:E13 C14:D23 D24:D32 C24:C56 Z57:XFD1048576">
-    <cfRule type="cellIs" dxfId="67" priority="252" operator="equal">
+  <conditionalFormatting sqref="A2:B56">
+    <cfRule type="cellIs" dxfId="66" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F32">
-    <cfRule type="cellIs" dxfId="66" priority="58" operator="equal">
+  <conditionalFormatting sqref="A57:W1048576 A1:W1 P7 AB7:XFD7 C7:E7 D14:D32 Z57:XFD1048576 D8:E13 C8:C56">
+    <cfRule type="cellIs" dxfId="65" priority="252" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="65" priority="1040"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="64" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F32">
+    <cfRule type="duplicateValues" dxfId="60" priority="1040"/>
+    <cfRule type="cellIs" dxfId="59" priority="58" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="64" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33:F50 Q7:Q56 P33:P34 AB33:XFD34 P39:P46 AB39:XFD46 P48:P50 AB48:XFD50">
-    <cfRule type="cellIs" dxfId="63" priority="119" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="119" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33:F50">
-    <cfRule type="duplicateValues" dxfId="62" priority="1019"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:F52">
-    <cfRule type="duplicateValues" dxfId="59" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="duplicateValues" dxfId="58" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="57" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57:W1048576 W1">
-    <cfRule type="duplicateValues" dxfId="51" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X55">
-    <cfRule type="duplicateValues" dxfId="50" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7">
-    <cfRule type="cellIs" dxfId="46" priority="82" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-    <cfRule type="duplicateValues" dxfId="45" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y8">
-    <cfRule type="duplicateValues" dxfId="44" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y8:Y13 Y22:Y32 Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="40" priority="1037"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y9:Y13 Y24:Y32 Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="39" priority="1034"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y9:Y13 Y24:Y32">
-    <cfRule type="duplicateValues" dxfId="38" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y14">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y15:Y19">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y20:Y21">
-    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y22:Y23">
-    <cfRule type="duplicateValues" dxfId="20" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y24:Y32">
-    <cfRule type="duplicateValues" dxfId="15" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:XFD1">
-    <cfRule type="cellIs" dxfId="14" priority="238" operator="equal">
+    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
+    <cfRule type="cellIs" dxfId="39" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA56">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+  <conditionalFormatting sqref="Y8">
+    <cfRule type="duplicateValues" dxfId="38" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y8:Y13 Y22:Y32 Y15:Y19">
+    <cfRule type="duplicateValues" dxfId="34" priority="1037"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y9:Y13 Y24:Y32 Y15:Y19">
+    <cfRule type="duplicateValues" dxfId="33" priority="1034"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y9:Y13 Y24:Y32">
+    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y14">
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y15:Y19">
+    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y20:Y21">
+    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y22:Y23">
+    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y24:Y32">
+    <cfRule type="duplicateValues" dxfId="9" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1:XFD1">
+    <cfRule type="cellIs" dxfId="8" priority="238" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B56">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
+  <conditionalFormatting sqref="AA2:AA56">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -8460,15 +8448,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -8533,7 +8521,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -8598,7 +8586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -8680,27 +8668,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.53515625" style="35" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="35" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="35" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.28515625" style="33"/>
+    <col min="9" max="9" width="18.15234375" style="35" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.3046875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="29" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="29" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
         <v>10</v>
       </c>
@@ -8745,12 +8733,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C2" s="47" t="s">
         <v>79</v>
@@ -8765,13 +8753,13 @@
         <v>289</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2" s="48" t="s">
         <v>80</v>
       </c>
       <c r="I2" s="41" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J2" s="51" t="s">
         <v>9</v>
@@ -8810,15 +8798,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>0</v>
       </c>
@@ -8841,7 +8829,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
